--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742577</v>
+        <v>122742578</v>
       </c>
       <c r="B2" t="n">
-        <v>78498</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Sörklubben N, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699556</v>
+        <v>699600</v>
       </c>
       <c r="R2" t="n">
-        <v>7063109</v>
+        <v>7063067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742578</v>
+        <v>122742577</v>
       </c>
       <c r="B3" t="n">
-        <v>90958</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörklubben N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699600</v>
+        <v>699556</v>
       </c>
       <c r="R3" t="n">
-        <v>7063067</v>
+        <v>7063109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742578</v>
+        <v>122742577</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörklubben N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699600</v>
+        <v>699556</v>
       </c>
       <c r="R2" t="n">
-        <v>7063067</v>
+        <v>7063109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742577</v>
+        <v>122742578</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Sörklubben N, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699556</v>
+        <v>699600</v>
       </c>
       <c r="R3" t="n">
-        <v>7063109</v>
+        <v>7063067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742577</v>
+        <v>122742578</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Sörklubben N, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699556</v>
+        <v>699600</v>
       </c>
       <c r="R2" t="n">
-        <v>7063109</v>
+        <v>7063067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742578</v>
+        <v>122742577</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörklubben N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699600</v>
+        <v>699556</v>
       </c>
       <c r="R3" t="n">
-        <v>7063067</v>
+        <v>7063109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742578</v>
+        <v>122742577</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörklubben N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699600</v>
+        <v>699556</v>
       </c>
       <c r="R2" t="n">
-        <v>7063067</v>
+        <v>7063109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742577</v>
+        <v>122742578</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Sörklubben N, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699556</v>
+        <v>699600</v>
       </c>
       <c r="R3" t="n">
-        <v>7063109</v>
+        <v>7063067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742577</v>
+        <v>122742578</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Sörklubben N, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699556</v>
+        <v>699600</v>
       </c>
       <c r="R2" t="n">
-        <v>7063109</v>
+        <v>7063067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742578</v>
+        <v>122742577</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörklubben N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699600</v>
+        <v>699556</v>
       </c>
       <c r="R3" t="n">
-        <v>7063067</v>
+        <v>7063109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742578</v>
+        <v>122742577</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>78505</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörklubben N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699600</v>
+        <v>699556</v>
       </c>
       <c r="R2" t="n">
-        <v>7063067</v>
+        <v>7063109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742577</v>
+        <v>122742578</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>90973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Sörklubben N, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699556</v>
+        <v>699600</v>
       </c>
       <c r="R3" t="n">
-        <v>7063109</v>
+        <v>7063067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742577</v>
+        <v>122742578</v>
       </c>
       <c r="B2" t="n">
-        <v>78505</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Sörklubben N, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699556</v>
+        <v>699600</v>
       </c>
       <c r="R2" t="n">
-        <v>7063109</v>
+        <v>7063067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742578</v>
+        <v>122742577</v>
       </c>
       <c r="B3" t="n">
-        <v>90973</v>
+        <v>78507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörklubben N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699600</v>
+        <v>699556</v>
       </c>
       <c r="R3" t="n">
-        <v>7063067</v>
+        <v>7063109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742578</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>122742577</v>
       </c>
       <c r="B3" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742578</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>122742577</v>
       </c>
       <c r="B3" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742578</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>122742577</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742578</v>
       </c>
       <c r="B2" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32524-2024 artfynd.xlsx
+++ b/artfynd/A 32524-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,8 +778,16 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122742577</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>